--- a/data/trending_integrated_20260923_12.xlsx
+++ b/data/trending_integrated_20260923_12.xlsx
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31495606748</v>
+        <v>31514669288</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18800</v>
+        <v>18260</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+21.13%</t>
+          <t>'+17.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>76210988025</v>
+        <v>78856736930</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14800</v>
+        <v>14630</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.85%</t>
+          <t>'+12.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>90</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>146797474130</v>
+        <v>148802300385</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18710</v>
+        <v>18410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.12%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G5" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>272504636590</v>
+        <v>276791053570</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -946,13 +946,13 @@
         <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="H6" t="n">
         <v>0.61</v>
@@ -978,7 +978,7 @@
         <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>61111104381</v>
+        <v>61383275696</v>
       </c>
       <c r="P6" t="n">
         <v>6300</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기 의혹 제기. 단기 단타장으로 변질된 시장에 대한 불만.</t>
+          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만. 단기 세력에 의한 시장 형성 우려.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['물량 떠넘기기', '단타', '상폐']</t>
+          <t>['급락', '물량 떠넘기기', '단타']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>218000</v>
+        <v>217500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F7" t="n">
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="H7" t="n">
         <v>75.51000000000001</v>
@@ -1070,7 +1070,7 @@
         <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>661981927000</v>
+        <v>669450933250</v>
       </c>
       <c r="P7" t="n">
         <v>243500</v>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G8" t="n">
-        <v>1888</v>
+        <v>1854</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1162,7 +1162,7 @@
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2626013033500</v>
+        <v>2676608775750</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대통령 및 정당 관련 정치적 언급과 함께 주가 상승 및 보유를 독려하는 의견이 혼재함. 단기적 주가 상승 기대 및 보유 의견이 있으나, 명확한 팩트 기반 근거는 부족함.</t>
+          <t>정치적 논쟁과 함께 개인 투자자들의 매수 심리 자극. 배당 기대감 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정치', '주가 상승', '보유']</t>
+          <t>['정치', '매수', '배당']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13920</v>
+        <v>13910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.28%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1254,7 +1254,7 @@
         <v>9.77</v>
       </c>
       <c r="O9" t="n">
-        <v>90777054530</v>
+        <v>91476341425</v>
       </c>
       <c r="P9" t="n">
         <v>23550</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1847000</v>
+        <v>8520</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.38%</t>
+          <t>'+0.59%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>94</v>
       </c>
       <c r="F10" t="n">
-        <v>505</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>1627</v>
+        <v>274</v>
       </c>
       <c r="H10" t="n">
-        <v>50.15</v>
+        <v>26.63</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1840000</v>
+        <v>8470</v>
       </c>
       <c r="K10" t="n">
-        <v>1899000</v>
+        <v>8510</v>
       </c>
       <c r="L10" t="n">
-        <v>1900000</v>
+        <v>8870</v>
       </c>
       <c r="M10" t="n">
-        <v>1836000</v>
+        <v>8480</v>
       </c>
       <c r="N10" t="n">
-        <v>50.17</v>
+        <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>3078106225000</v>
+        <v>19988451475</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>17950</v>
       </c>
       <c r="Q10" t="n">
-        <v>333000</v>
+        <v>8120</v>
       </c>
       <c r="R10" t="n">
-        <v>-103000</v>
+        <v>353000</v>
       </c>
       <c r="S10" t="n">
-        <v>106000</v>
+        <v>-6000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>국내 증시의 신뢰도 부족과 주가 관리 문제 제기. 해외 반도체 기업과의 비교 및 기관 매도세에 대한 우려.</t>
+          <t>유리 기판 사업 경쟁력 강화와 실적 개선 전망. 목표 주가 하향 리포트에 대한 불신 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['국장', '주가 관리', '외인']</t>
+          <t>['유리 기판', '커스텀 공정', '실적']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8480</v>
+        <v>1846000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>498</v>
       </c>
       <c r="G11" t="n">
-        <v>270</v>
+        <v>1605</v>
       </c>
       <c r="H11" t="n">
-        <v>26.63</v>
+        <v>50.15</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8470</v>
+        <v>1840000</v>
       </c>
       <c r="K11" t="n">
-        <v>8510</v>
+        <v>1899000</v>
       </c>
       <c r="L11" t="n">
-        <v>8870</v>
+        <v>1900000</v>
       </c>
       <c r="M11" t="n">
-        <v>8480</v>
+        <v>1836000</v>
       </c>
       <c r="N11" t="n">
-        <v>26.58</v>
+        <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>19804574575</v>
+        <v>3157636884000</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>8120</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>353000</v>
+        <v>-103000</v>
       </c>
       <c r="S11" t="n">
-        <v>-6000</v>
+        <v>106000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>유리 기판 사업 경쟁력 강화와 실적 개선 전망. 목표 주가 하향 리포트에 대한 불신 존재.</t>
+          <t>국내 증시 전반의 신뢰도 문제 제기. 반도체 업황 및 외국인 매매 동향에 대한 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['유리 기판', '커스텀 공정', '실적']</t>
+          <t>['국내 증시', '반도체', '외국인']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,86 +1476,86 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>31100</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'+0.16%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E12" t="n">
+        <v>259</v>
+      </c>
+      <c r="F12" t="n">
+        <v>170</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1578</v>
+      </c>
+      <c r="H12" t="n">
+        <v>16.63</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>31050</v>
+      </c>
+      <c r="K12" t="n">
         <v>31300</v>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>'-0.32%</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E12" t="n">
-        <v>48</v>
-      </c>
-      <c r="F12" t="n">
-        <v>33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>127</v>
-      </c>
-      <c r="H12" t="n">
-        <v>52.81</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>31400</v>
-      </c>
-      <c r="K12" t="n">
-        <v>31500</v>
-      </c>
       <c r="L12" t="n">
-        <v>32100</v>
+        <v>31550</v>
       </c>
       <c r="M12" t="n">
-        <v>31100</v>
+        <v>30050</v>
       </c>
       <c r="N12" t="n">
-        <v>25.75</v>
+        <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>81434969200</v>
+        <v>8177934625</v>
       </c>
       <c r="P12" t="n">
-        <v>32100</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>21000</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>-6000</v>
+        <v>-51000</v>
       </c>
       <c r="S12" t="n">
-        <v>51000</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>미국 FDA 신약 승인 기대감 및 간암, 담관암 관련 긍정적 전망. 릴레이테라퓨틱스 상승 및 공매도 세력 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['신약 승인', 'FDA', '간암']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17720</v>
+        <v>17700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.51%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.76</v>
       </c>
       <c r="E13" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="H13" t="n">
         <v>5.46</v>
@@ -1622,7 +1622,7 @@
         <v>6.22</v>
       </c>
       <c r="O13" t="n">
-        <v>119770380235</v>
+        <v>120403122590</v>
       </c>
       <c r="P13" t="n">
         <v>31500</v>
@@ -1667,11 +1667,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30850</v>
+        <v>31200</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,67 +1679,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.21</v>
+        <v>0.62</v>
       </c>
       <c r="E14" t="n">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>168</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>1562</v>
+        <v>127</v>
       </c>
       <c r="H14" t="n">
-        <v>16.63</v>
+        <v>52.81</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31050</v>
+        <v>31400</v>
       </c>
       <c r="K14" t="n">
-        <v>31300</v>
+        <v>31500</v>
       </c>
       <c r="L14" t="n">
-        <v>31550</v>
+        <v>32100</v>
       </c>
       <c r="M14" t="n">
-        <v>30050</v>
+        <v>31100</v>
       </c>
       <c r="N14" t="n">
-        <v>16.42</v>
+        <v>25.75</v>
       </c>
       <c r="O14" t="n">
-        <v>7825239525</v>
+        <v>83118399700</v>
       </c>
       <c r="P14" t="n">
-        <v>69200</v>
+        <v>32100</v>
       </c>
       <c r="Q14" t="n">
-        <v>24150</v>
+        <v>21000</v>
       </c>
       <c r="R14" t="n">
-        <v>-51000</v>
+        <v>-6000</v>
       </c>
       <c r="S14" t="n">
-        <v>-1000</v>
+        <v>51000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 FDA 신약 승인 기대감 및 간암, 담관암 관련 긍정적 전망. 릴레이테라퓨틱스 상승 및 공매도 세력 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신약 승인', 'FDA', '간암']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30700</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
         <v>112</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>65602264000</v>
+        <v>66293776675</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1866,13 +1866,13 @@
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>66617851150</v>
+        <v>66796109825</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 '세계 최고 헬스테크 기업'이라는 긍정적 뉴스를 기반으로 주가 상승 기대감이 있으나, 실제 주가 움직임에 대한 실망감과 변동성에 대한 언급도 나타남. 보유 및 기다림을 강조하는 의견이 있음.</t>
+          <t>타임지 선정 등 호재에도 불구하고 주가 부진. 주가 조작 의혹 및 개인 투자자들의 실망감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['헬스테크', '타임지', '주가 상승']</t>
+          <t>['타임지', '주가 부진', '주가 조작']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -1958,13 +1958,13 @@
         <v>-0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H17" t="n">
         <v>38.34</v>
@@ -1990,7 +1990,7 @@
         <v>38.44</v>
       </c>
       <c r="O17" t="n">
-        <v>68562193775</v>
+        <v>69412648750</v>
       </c>
       <c r="P17" t="n">
         <v>67300</v>
@@ -2035,83 +2035,83 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>81400</v>
+        <v>2725</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-5.55%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.02</v>
+        <v>0.92</v>
       </c>
       <c r="E18" t="n">
-        <v>550</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>312</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>1574</v>
+        <v>200</v>
       </c>
       <c r="H18" t="n">
-        <v>23.03</v>
+        <v>1.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>86500</v>
+        <v>2885</v>
       </c>
       <c r="K18" t="n">
-        <v>86100</v>
+        <v>3000</v>
       </c>
       <c r="L18" t="n">
-        <v>86100</v>
+        <v>3480</v>
       </c>
       <c r="M18" t="n">
-        <v>80500</v>
+        <v>2685</v>
       </c>
       <c r="N18" t="n">
-        <v>23.05</v>
+        <v>0.48</v>
       </c>
       <c r="O18" t="n">
-        <v>226526599700</v>
+        <v>21453034612</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>4760</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>973</v>
       </c>
       <c r="R18" t="n">
-        <v>-486000</v>
+        <v>-227000</v>
       </c>
       <c r="S18" t="n">
-        <v>-68000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>한국형 원전 수주 기대감 속 개인 투자자들의 불안감과 실망감 표출. 외인, 기관, 연기금 매도세 확인.</t>
+          <t>유상증자 및 경영권 변경 이슈에 대한 투자자들의 불신. 차트 조작 및 하한가 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['원전', 'SMR', '조정']</t>
+          <t>['유상증자', '경영권 변경', '하한가']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2705</v>
+        <v>81300</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.24%</t>
+          <t>'-6.01%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.92</v>
+        <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>84</v>
+        <v>558</v>
       </c>
       <c r="F19" t="n">
-        <v>48</v>
+        <v>314</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>1604</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4</v>
+        <v>23.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2885</v>
+        <v>86500</v>
       </c>
       <c r="K19" t="n">
-        <v>3000</v>
+        <v>86100</v>
       </c>
       <c r="L19" t="n">
-        <v>3480</v>
+        <v>86100</v>
       </c>
       <c r="M19" t="n">
-        <v>2685</v>
+        <v>80500</v>
       </c>
       <c r="N19" t="n">
-        <v>0.48</v>
+        <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>21294965255</v>
+        <v>228133953550</v>
       </c>
       <c r="P19" t="n">
-        <v>4760</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>973</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-227000</v>
+        <v>-486000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-68000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>유상증자 및 최대 주주 변경 관련 의혹 제기. 경영권 변경 및 투자자 보호 문제에 대한 우려.</t>
+          <t>원전 관련 호재에도 불구하고 주가 하락. 투자자들의 불만 고조.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['유상증자', '경영권 변경', '배정']</t>
+          <t>['원전', '주가 하락', '불만']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17590</v>
+        <v>17600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.44%</t>
+          <t>'-6.38%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F20" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G20" t="n">
-        <v>804</v>
+        <v>828</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>119508434080</v>
+        <v>120511902485</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력의 파산 가능성과 대차 해지 운동 독려. 단, 구체적인 근거는 불명확.</t>
+          <t>공매도 세력과의 갈등 심화. 공매도 파산 가능성 및 대차 해지 운동 촉구.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지', '신속심의']</t>
+          <t>['공매도', '대차', '주가 조작']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260923_12.xlsx
+++ b/data/trending_integrated_20260923_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31514669288</v>
+        <v>31526736203</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18260</v>
+        <v>18500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.65%</t>
+          <t>'+19.20%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>78856736930</v>
+        <v>80104801470</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14630</v>
+        <v>14510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+12.54%</t>
+          <t>'+11.62%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H4" t="n">
         <v>0.86</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>148802300385</v>
+        <v>150408904900</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18410</v>
+        <v>18450</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.31%</t>
+          <t>'+11.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G5" t="n">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>276791053570</v>
+        <v>281018554265</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등에 따른 기대감. 아이온큐 급등 및 양자 보안 관련 장비 언급. 공매도 세력에 대한 경계.</t>
+          <t>미국 양자 관련주 급등 소식이 전해지며 긍정적인 기대감이 형성되고 있습니다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자 보안', '아이온큐', '공매도']</t>
+          <t>['양자', '급등', '기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3860</v>
+        <v>217500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.62%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.35</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>68</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="H6" t="n">
-        <v>0.61</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3725</v>
+        <v>211500</v>
       </c>
       <c r="K6" t="n">
-        <v>3740</v>
+        <v>217000</v>
       </c>
       <c r="L6" t="n">
-        <v>4200</v>
+        <v>220000</v>
       </c>
       <c r="M6" t="n">
-        <v>3705</v>
+        <v>216500</v>
       </c>
       <c r="N6" t="n">
-        <v>0.96</v>
+        <v>75.5</v>
       </c>
       <c r="O6" t="n">
-        <v>61383275696</v>
+        <v>686929179500</v>
       </c>
       <c r="P6" t="n">
-        <v>6300</v>
+        <v>243500</v>
       </c>
       <c r="Q6" t="n">
-        <v>1738</v>
+        <v>65000</v>
       </c>
       <c r="R6" t="n">
-        <v>-41000</v>
+        <v>753000</v>
       </c>
       <c r="S6" t="n">
-        <v>-5000</v>
+        <v>-47000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만. 단기 세력에 의한 시장 형성 우려.</t>
+          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['급락', '물량 떠넘기기', '단타']</t>
+          <t>['배당', '우선주', '장기보유']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217500</v>
+        <v>13930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>311</v>
+        <v>197</v>
       </c>
       <c r="H7" t="n">
-        <v>75.51000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>211500</v>
+        <v>13600</v>
       </c>
       <c r="K7" t="n">
-        <v>217000</v>
+        <v>13750</v>
       </c>
       <c r="L7" t="n">
-        <v>220000</v>
+        <v>15050</v>
       </c>
       <c r="M7" t="n">
-        <v>216500</v>
+        <v>13740</v>
       </c>
       <c r="N7" t="n">
-        <v>75.5</v>
+        <v>9.77</v>
       </c>
       <c r="O7" t="n">
-        <v>669450933250</v>
+        <v>91991609840</v>
       </c>
       <c r="P7" t="n">
-        <v>243500</v>
+        <v>23550</v>
       </c>
       <c r="Q7" t="n">
-        <v>65000</v>
+        <v>5780</v>
       </c>
       <c r="R7" t="n">
-        <v>753000</v>
+        <v>180000</v>
       </c>
       <c r="S7" t="n">
-        <v>-47000</v>
+        <v>-194000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '장기보유']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G8" t="n">
-        <v>1854</v>
+        <v>1902</v>
       </c>
       <c r="H8" t="n">
         <v>46.55</v>
@@ -1162,7 +1162,7 @@
         <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>2676608775750</v>
+        <v>2762961465000</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 논쟁과 함께 개인 투자자들의 매수 심리 자극. 배당 기대감 언급.</t>
+          <t>정치적 발언과 함께 주가 상승 기대감이 혼재되어 있으며, 배당 관련 문의가 나타납니다.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['정치', '매수', '배당']</t>
+          <t>['배당', '상승', '정치']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,92 +1207,92 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13910</v>
+        <v>3785</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.28%</t>
+          <t>'+1.61%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.16</v>
+        <v>-0.35</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>119</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="G9" t="n">
-        <v>194</v>
+        <v>330</v>
       </c>
       <c r="H9" t="n">
-        <v>9.609999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13600</v>
+        <v>3725</v>
       </c>
       <c r="K9" t="n">
-        <v>13750</v>
+        <v>3740</v>
       </c>
       <c r="L9" t="n">
-        <v>15050</v>
+        <v>4200</v>
       </c>
       <c r="M9" t="n">
-        <v>13740</v>
+        <v>3705</v>
       </c>
       <c r="N9" t="n">
-        <v>9.77</v>
+        <v>0.96</v>
       </c>
       <c r="O9" t="n">
-        <v>91476341425</v>
+        <v>62705877721</v>
       </c>
       <c r="P9" t="n">
-        <v>23550</v>
+        <v>6300</v>
       </c>
       <c r="Q9" t="n">
-        <v>5780</v>
+        <v>1738</v>
       </c>
       <c r="R9" t="n">
-        <v>180000</v>
+        <v>-41000</v>
       </c>
       <c r="S9" t="n">
-        <v>-194000</v>
+        <v>-5000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만. 단기 세력에 의한 시장 형성 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['급락', '물량 떠넘기기', '단타']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8520</v>
+        <v>8530</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.59%</t>
+          <t>'+0.71%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>19988451475</v>
+        <v>20195119620</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리 기판 사업 경쟁력 강화와 실적 개선 전망. 목표 주가 하향 리포트에 대한 불신 존재.</t>
+          <t>유리 기판 사업 관련 긍정적 내용과 함께, 증권사 리포트 및 외국인 수급에 대한 불신이 교차합니다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리 기판', '커스텀 공정', '실적']</t>
+          <t>['유리기판', '리포트', '외국인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1846000</v>
+        <v>1848000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.43%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G11" t="n">
-        <v>1605</v>
+        <v>1620</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3157636884000</v>
+        <v>3234103107000</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 전반의 신뢰도 문제 제기. 반도체 업황 및 외국인 매매 동향에 대한 언급.</t>
+          <t>증시 전반에 대한 불신과 함께, 반도체 섹터의 부진 및 기관 매도에 대한 부정적 의견이 많습니다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['국내 증시', '반도체', '외국인']</t>
+          <t>['반도체', '국장', '기관']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G12" t="n">
-        <v>1578</v>
+        <v>1588</v>
       </c>
       <c r="H12" t="n">
         <v>16.63</v>
@@ -1530,7 +1530,7 @@
         <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>8177934625</v>
+        <v>8549615225</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1575,184 +1575,184 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17700</v>
+        <v>31200</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'-0.64%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.76</v>
+        <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>730</v>
+        <v>132</v>
       </c>
       <c r="H13" t="n">
-        <v>5.46</v>
+        <v>52.81</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17810</v>
+        <v>31400</v>
       </c>
       <c r="K13" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="L13" t="n">
-        <v>18180</v>
+        <v>32100</v>
       </c>
       <c r="M13" t="n">
-        <v>17410</v>
+        <v>31100</v>
       </c>
       <c r="N13" t="n">
-        <v>6.22</v>
+        <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>120403122590</v>
+        <v>83961760875</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>32100</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>21000</v>
       </c>
       <c r="R13" t="n">
-        <v>-260000</v>
+        <v>-6000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>51000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>추석 연휴 전 주가 상승 기대감과 2만원 돌파 시도. 쇼티지 현상 및 외국인 매수세 전환 가능성 언급.</t>
+          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['쇼티지', '2만원', '광섹터']</t>
+          <t>['영업이익', '합병', '인천공항']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31200</v>
+        <v>17660</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-0.84%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.62</v>
+        <v>-0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="G14" t="n">
-        <v>127</v>
+        <v>732</v>
       </c>
       <c r="H14" t="n">
-        <v>52.81</v>
+        <v>5.46</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>31400</v>
+        <v>17810</v>
       </c>
       <c r="K14" t="n">
+        <v>17950</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18180</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17410</v>
+      </c>
+      <c r="N14" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="O14" t="n">
+        <v>121657939990</v>
+      </c>
+      <c r="P14" t="n">
         <v>31500</v>
       </c>
-      <c r="L14" t="n">
-        <v>32100</v>
-      </c>
-      <c r="M14" t="n">
-        <v>31100</v>
-      </c>
-      <c r="N14" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="O14" t="n">
-        <v>83118399700</v>
-      </c>
-      <c r="P14" t="n">
-        <v>32100</v>
-      </c>
       <c r="Q14" t="n">
-        <v>21000</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-6000</v>
+        <v>-260000</v>
       </c>
       <c r="S14" t="n">
-        <v>51000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>인천공항 이용객 증가 및 내년 영업이익 전망 제시, 합병 효과는 장기적 관점.</t>
+          <t>2만원 돌파 기대감과 함께 단기적인 상승 및 외국인 수급 변화에 대한 언급이 있습니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['영업이익', '합병', '인천공항']</t>
+          <t>['2만원', '상승', '외국인']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -1774,10 +1774,10 @@
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
         <v>112</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>66293776675</v>
+        <v>67112732825</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23250</v>
+        <v>23100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G16" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>66796109825</v>
+        <v>67155251350</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 등 호재에도 불구하고 주가 부진. 주가 조작 의혹 및 개인 투자자들의 실망감.</t>
+          <t>타임지 선정 소식에도 불구하고 주가 부진에 대한 실망감이 나타나며, 향후 추세에 대한 관망세가 짙습니다.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['타임지', '주가 부진', '주가 조작']</t>
+          <t>['타임지', '주가 부진', '추세']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,70 +1943,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48750</v>
+        <v>2770</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1</v>
+        <v>0.92</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F17" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="H17" t="n">
-        <v>38.34</v>
+        <v>1.4</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>51200</v>
+        <v>2885</v>
       </c>
       <c r="K17" t="n">
-        <v>51600</v>
+        <v>3000</v>
       </c>
       <c r="L17" t="n">
-        <v>51600</v>
+        <v>3480</v>
       </c>
       <c r="M17" t="n">
-        <v>48600</v>
+        <v>2685</v>
       </c>
       <c r="N17" t="n">
-        <v>38.44</v>
+        <v>0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>69412648750</v>
+        <v>21616055567</v>
       </c>
       <c r="P17" t="n">
-        <v>67300</v>
+        <v>4760</v>
       </c>
       <c r="Q17" t="n">
-        <v>23150</v>
+        <v>973</v>
       </c>
       <c r="R17" t="n">
-        <v>-262000</v>
+        <v>-227000</v>
       </c>
       <c r="S17" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 장난질 의혹 제기. LNG 플랜트 관련 사업 내용 언급.</t>
+          <t>유상증자 및 경영권 변경에 대한 혼란 속에서, 일부는 매수를 시도하고 일부는 우려를 표합니다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['LNG 플랜트', '장난질', '20일선']</t>
+          <t>['유상증자', '경영권', '매수']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2725</v>
+        <v>48700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.55%</t>
+          <t>'-4.88%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.92</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4</v>
+        <v>38.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2885</v>
+        <v>51200</v>
       </c>
       <c r="K18" t="n">
-        <v>3000</v>
+        <v>51600</v>
       </c>
       <c r="L18" t="n">
-        <v>3480</v>
+        <v>51600</v>
       </c>
       <c r="M18" t="n">
-        <v>2685</v>
+        <v>48600</v>
       </c>
       <c r="N18" t="n">
-        <v>0.48</v>
+        <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>21453034612</v>
+        <v>70983968675</v>
       </c>
       <c r="P18" t="n">
-        <v>4760</v>
+        <v>67300</v>
       </c>
       <c r="Q18" t="n">
-        <v>973</v>
+        <v>23150</v>
       </c>
       <c r="R18" t="n">
-        <v>-227000</v>
+        <v>-262000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>유상증자 및 경영권 변경 이슈에 대한 투자자들의 불신. 차트 조작 및 하한가 언급.</t>
+          <t>주가 하락에 대한 불만이 고조되며, 6개월간의 보유 기간에도 불구하고 부정적인 전망이 지배적입니다.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['유상증자', '경영권 변경', '하한가']</t>
+          <t>['주가 하락', '6개월', '기대']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>028050</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81300</v>
+        <v>81400</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.01%</t>
+          <t>'-5.90%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>558</v>
+        <v>566</v>
       </c>
       <c r="F19" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G19" t="n">
-        <v>1604</v>
+        <v>1637</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2174,7 +2174,7 @@
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>228133953550</v>
+        <v>232864043700</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 관련 호재에도 불구하고 주가 하락. 투자자들의 불만 고조.</t>
+          <t>미국 원전 수주 기대감에도 불구하고, 외인·기관 매도 및 차트 붕괴 우려가 제기됩니다.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '주가 하락', '불만']</t>
+          <t>['원전', '수주', '매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17600</v>
+        <v>17590</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.38%</t>
+          <t>'-6.44%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F20" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G20" t="n">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>120511902485</v>
+        <v>121713150855</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>

--- a/data/trending_integrated_20260923_12.xlsx
+++ b/data/trending_integrated_20260923_12.xlsx
@@ -584,7 +584,7 @@
         <v>36</v>
       </c>
       <c r="G2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31526736203</v>
+        <v>31546900823</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18500</v>
+        <v>18110</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+19.20%</t>
+          <t>'+16.69%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>80104801470</v>
+        <v>80835073760</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>NASA 선정 및 스페이스X 협력에 따른 초소형 X-ray 기술력 검증. 인도발 수주 재료와 함께 시총 1조 기대감 고조.</t>
+          <t>스페이스X, NASA 선정 등 복합적인 호재로 인한 급등 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['X-ray', 'NASA', '스페이스X']</t>
+          <t>['스페이스X', 'NASA', '엑스레이']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14510</v>
+        <v>14720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.62%</t>
+          <t>'+13.23%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" t="n">
         <v>0.86</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>150408904900</v>
+        <v>152232745810</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18450</v>
+        <v>18230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.55%</t>
+          <t>'+10.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F5" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="G5" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>281018554265</v>
+        <v>283370161310</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>217500</v>
+        <v>218000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+3.07%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="H6" t="n">
         <v>75.51000000000001</v>
@@ -978,7 +978,7 @@
         <v>75.5</v>
       </c>
       <c r="O6" t="n">
-        <v>686929179500</v>
+        <v>696210155750</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13930</v>
+        <v>283000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.43%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>41</v>
+        <v>481</v>
       </c>
       <c r="G7" t="n">
-        <v>197</v>
+        <v>1875</v>
       </c>
       <c r="H7" t="n">
-        <v>9.609999999999999</v>
+        <v>46.55</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,71 +1055,71 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13600</v>
+        <v>276500</v>
       </c>
       <c r="K7" t="n">
-        <v>13750</v>
+        <v>284500</v>
       </c>
       <c r="L7" t="n">
-        <v>15050</v>
+        <v>285000</v>
       </c>
       <c r="M7" t="n">
-        <v>13740</v>
+        <v>281000</v>
       </c>
       <c r="N7" t="n">
-        <v>9.77</v>
+        <v>46.56</v>
       </c>
       <c r="O7" t="n">
-        <v>91991609840</v>
+        <v>2842817437250</v>
       </c>
       <c r="P7" t="n">
-        <v>23550</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>5780</v>
+        <v>82400</v>
       </c>
       <c r="R7" t="n">
-        <v>180000</v>
+        <v>1744000</v>
       </c>
       <c r="S7" t="n">
-        <v>-194000</v>
+        <v>499000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>총선 관련 정치적 발언과 함께 주가 상승 기대 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>283000</v>
+        <v>13920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1127,19 +1127,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.01</v>
+        <v>-0.16</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>478</v>
+        <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>1902</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
-        <v>46.55</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,60 +1147,60 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>276500</v>
+        <v>13600</v>
       </c>
       <c r="K8" t="n">
-        <v>284500</v>
+        <v>13750</v>
       </c>
       <c r="L8" t="n">
-        <v>285000</v>
+        <v>15050</v>
       </c>
       <c r="M8" t="n">
-        <v>281000</v>
+        <v>13740</v>
       </c>
       <c r="N8" t="n">
-        <v>46.56</v>
+        <v>9.77</v>
       </c>
       <c r="O8" t="n">
-        <v>2762961465000</v>
+        <v>92401788490</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>23550</v>
       </c>
       <c r="Q8" t="n">
-        <v>82400</v>
+        <v>5780</v>
       </c>
       <c r="R8" t="n">
-        <v>1744000</v>
+        <v>180000</v>
       </c>
       <c r="S8" t="n">
-        <v>499000</v>
+        <v>-194000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 주가 상승 기대감이 혼재되어 있으며, 배당 관련 문의가 나타납니다.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['배당', '상승', '정치']</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3785</v>
+        <v>3800</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.61%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.35</v>
       </c>
       <c r="E9" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G9" t="n">
-        <v>330</v>
+        <v>350</v>
       </c>
       <c r="H9" t="n">
         <v>0.61</v>
@@ -1254,7 +1254,7 @@
         <v>0.96</v>
       </c>
       <c r="O9" t="n">
-        <v>62705877721</v>
+        <v>63080186290</v>
       </c>
       <c r="P9" t="n">
         <v>6300</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>급격한 주가 하락 및 물량 떠넘기기에 대한 불만. 단기 세력에 의한 시장 형성 우려.</t>
+          <t>주가 급락 및 물량 넘기기에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['급락', '물량 떠넘기기', '단타']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8530</v>
+        <v>8535</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.71%</t>
+          <t>'+0.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>20195119620</v>
+        <v>20445736225</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리 기판 사업 관련 긍정적 내용과 함께, 증권사 리포트 및 외국인 수급에 대한 불신이 교차합니다.</t>
+          <t>유리기판 사업 관련 긍정적 전망과 함께 키움증권의 매매 패턴 분석.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '리포트', '외국인']</t>
+          <t>['유리기판', '디스플레이']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1848000</v>
+        <v>1849000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.43%</t>
+          <t>'+0.49%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>497</v>
+        <v>490</v>
       </c>
       <c r="G11" t="n">
-        <v>1620</v>
+        <v>1653</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3234103107000</v>
+        <v>3310737724500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>증시 전반에 대한 불신과 함께, 반도체 섹터의 부진 및 기관 매도에 대한 부정적 의견이 많습니다.</t>
+          <t>국내 증시 신뢰도 하락 및 SK하이닉스 주가 부진에 대한 불만 토로.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['반도체', '국장', '기관']</t>
+          <t>['ADR', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="F12" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G12" t="n">
-        <v>1588</v>
+        <v>1614</v>
       </c>
       <c r="H12" t="n">
         <v>16.63</v>
@@ -1530,7 +1530,7 @@
         <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>8549615225</v>
+        <v>9078555975</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31200</v>
+        <v>31250</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.64%</t>
+          <t>'-0.48%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,7 +1596,7 @@
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H13" t="n">
         <v>52.81</v>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>83961760875</v>
+        <v>85689837900</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17660</v>
+        <v>17640</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.84%</t>
+          <t>'-0.95%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="H14" t="n">
         <v>5.46</v>
@@ -1714,7 +1714,7 @@
         <v>6.22</v>
       </c>
       <c r="O14" t="n">
-        <v>121657939990</v>
+        <v>122727604755</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>2만원 돌파 기대감과 함께 단기적인 상승 및 외국인 수급 변화에 대한 언급이 있습니다.</t>
+          <t>추석 연휴 전 주가 상승 기대감 및 단타 세력의 이탈 촉구.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['2만원', '상승', '외국인']</t>
+          <t>['쇼티지', '광통신']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30750</v>
+        <v>30850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.69%</t>
+          <t>'-2.37%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" t="n">
         <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>67112732825</v>
+        <v>67955515425</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23100</v>
+        <v>23200</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-3.13%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>67155251350</v>
+        <v>67321975125</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 소식에도 불구하고 주가 부진에 대한 실망감이 나타나며, 향후 추세에 대한 관망세가 짙습니다.</t>
+          <t>타임지 선정 및 헬스케어 기술 관련 기대감, 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['타임지', '주가 부진', '추세']</t>
+          <t>['헬스케어', '타임지']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2770</v>
+        <v>2765</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.92</v>
       </c>
       <c r="E17" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H17" t="n">
         <v>1.4</v>
@@ -1990,7 +1990,7 @@
         <v>0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>21616055567</v>
+        <v>21692731257</v>
       </c>
       <c r="P17" t="n">
         <v>4760</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48700</v>
+        <v>48750</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-4.79%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F18" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="H18" t="n">
         <v>38.34</v>
@@ -2082,7 +2082,7 @@
         <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>70983968675</v>
+        <v>71829425400</v>
       </c>
       <c r="P18" t="n">
         <v>67300</v>
@@ -2142,13 +2142,13 @@
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F19" t="n">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="G19" t="n">
-        <v>1637</v>
+        <v>1616</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2174,7 +2174,7 @@
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>232864043700</v>
+        <v>238826426550</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 원전 수주 기대감에도 불구하고, 외인·기관 매도 및 차트 붕괴 우려가 제기됩니다.</t>
+          <t>원전 관련 호재에도 불구하고 주가 하락 및 외인/기관 매도세 우려.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '수주', '매도']</t>
+          <t>['원전', 'SMR']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F20" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G20" t="n">
-        <v>814</v>
+        <v>857</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>121713150855</v>
+        <v>122687185340</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력과의 갈등 심화. 공매도 파산 가능성 및 대차 해지 운동 촉구.</t>
+          <t>공매도 세력과의 전쟁 선포 및 파산 기대감 표출.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '주가 조작']</t>
+          <t>['공매도', '대차해지']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260923_12.xlsx
+++ b/data/trending_integrated_20260923_12.xlsx
@@ -578,13 +578,13 @@
         <v>-1.02</v>
       </c>
       <c r="E2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H2" t="n">
         <v>1.63</v>
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31546900823</v>
+        <v>31554236543</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18110</v>
+        <v>18160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.69%</t>
+          <t>'+17.01%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>134</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>80835073760</v>
+        <v>81647639535</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>스페이스X, NASA 선정 등 복합적인 호재로 인한 급등 기대감.</t>
+          <t>스페이스X, NASA 선정 등 긍정적인 재료가 부각되며 주가 급등에 대한 기대감이 높음.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['스페이스X', 'NASA', '엑스레이']</t>
+          <t>['스페이스X', 'NASA', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14720</v>
+        <v>14520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+13.23%</t>
+          <t>'+11.69%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H4" t="n">
         <v>0.86</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>152232745810</v>
+        <v>153261381340</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18230</v>
+        <v>18370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+10.22%</t>
+          <t>'+11.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F5" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G5" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>283370161310</v>
+        <v>285789843640</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>미국 양자 관련주 급등 소식이 전해지며 긍정적인 기대감이 형성되고 있습니다.</t>
+          <t>미국 증시의 양자 관련주 급등 소식과 함께 엑스게이트의 상승 기대감이 나타남.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['양자', '급등', '기대']</t>
+          <t>['양자보안', '급등', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,13 +946,13 @@
         <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="H6" t="n">
         <v>75.51000000000001</v>
@@ -978,7 +978,7 @@
         <v>75.5</v>
       </c>
       <c r="O6" t="n">
-        <v>696210155750</v>
+        <v>711734515500</v>
       </c>
       <c r="P6" t="n">
         <v>243500</v>
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>283000</v>
+        <v>283250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.44%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="G7" t="n">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="H7" t="n">
         <v>46.55</v>
@@ -1070,7 +1070,7 @@
         <v>46.56</v>
       </c>
       <c r="O7" t="n">
-        <v>2842817437250</v>
+        <v>2886839674750</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>총선 관련 정치적 발언과 함께 주가 상승 기대 언급.</t>
+          <t>정치적 발언과 함께 주가 상승 및 배당 관련 질문이 혼재됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['배당', '주가', '분석']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1136,7 +1136,7 @@
         <v>41</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H8" t="n">
         <v>9.609999999999999</v>
@@ -1162,7 +1162,7 @@
         <v>9.77</v>
       </c>
       <c r="O8" t="n">
-        <v>92401788490</v>
+        <v>92829086855</v>
       </c>
       <c r="P8" t="n">
         <v>23550</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3800</v>
+        <v>3780</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.35</v>
       </c>
       <c r="E9" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F9" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="H9" t="n">
         <v>0.61</v>
@@ -1254,7 +1254,7 @@
         <v>0.96</v>
       </c>
       <c r="O9" t="n">
-        <v>63080186290</v>
+        <v>63411007035</v>
       </c>
       <c r="P9" t="n">
         <v>6300</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8535</v>
+        <v>8550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.77%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F10" t="n">
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>20445736225</v>
+        <v>20647516100</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>유리기판 사업 관련 긍정적 전망과 함께 키움증권의 매매 패턴 분석.</t>
+          <t>키움증권의 매매 행태와 주가 하락에 대한 불만이 제기되며, 일부 긍정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['유리기판', '디스플레이']</t>
+          <t>['주가조작', '외인', '전망']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1849000</v>
+        <v>1855000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.49%</t>
+          <t>'+0.82%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G11" t="n">
-        <v>1653</v>
+        <v>1667</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3310737724500</v>
+        <v>3386353901500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시 신뢰도 하락 및 SK하이닉스 주가 부진에 대한 불만 토로.</t>
+          <t>국내 증시와 주가 관리 방식에 대한 불신이 강하게 나타나며, 반도체 시장과의 연동성 부족을 지적.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['ADR', '반도체']</t>
+          <t>['주가', '국장', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1498,13 +1498,13 @@
         <v>0.21</v>
       </c>
       <c r="E12" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F12" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G12" t="n">
-        <v>1614</v>
+        <v>1625</v>
       </c>
       <c r="H12" t="n">
         <v>16.63</v>
@@ -1530,7 +1530,7 @@
         <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>9078555975</v>
+        <v>9339041525</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1579,11 +1579,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>31250</v>
+        <v>31300</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-0.48%</t>
+          <t>'-0.32%</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1596,10 +1596,10 @@
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H13" t="n">
-        <v>52.81</v>
+        <v>52.8</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>85689837900</v>
+        <v>86806276450</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17640</v>
+        <v>17690</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.95%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1688,7 +1688,7 @@
         <v>75</v>
       </c>
       <c r="G14" t="n">
-        <v>736</v>
+        <v>763</v>
       </c>
       <c r="H14" t="n">
         <v>5.46</v>
@@ -1714,7 +1714,7 @@
         <v>6.22</v>
       </c>
       <c r="O14" t="n">
-        <v>122727604755</v>
+        <v>123459195660</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>추석 연휴 전 주가 상승 기대감 및 단타 세력의 이탈 촉구.</t>
+          <t>명절 전 주가 상승 기대감과 함께 단기 수익을 노리는 의견이 제시됨.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['쇼티지', '광통신']</t>
+          <t>['주포', '단타', '급등']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30850</v>
+        <v>30950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.37%</t>
+          <t>'-2.06%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>67955515425</v>
+        <v>68913188500</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23200</v>
+        <v>23150</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.13%</t>
+          <t>'-3.34%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F16" t="n">
         <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>67321975125</v>
+        <v>67417620675</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 및 헬스케어 기술 관련 기대감, 주가 상승 전망.</t>
+          <t>타임지 선정 소식과 함께 주가 상승에 대한 기대감이 있으나, 거래량 부족 및 주가 하락에 대한 우려도 존재.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['헬스케어', '타임지']</t>
+          <t>['타임지', '헬스테크', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,11 +1947,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2765</v>
+        <v>2780</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-3.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1964,7 +1964,7 @@
         <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H17" t="n">
         <v>1.4</v>
@@ -1990,7 +1990,7 @@
         <v>0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>21692731257</v>
+        <v>21731465807</v>
       </c>
       <c r="P17" t="n">
         <v>4760</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>유상증자 및 경영권 변경에 대한 혼란 속에서, 일부는 매수를 시도하고 일부는 우려를 표합니다.</t>
+          <t>유상증자, 최대주주 변경 등 부정적인 이슈가 부각되며 주가 하락 및 불안감이 나타남.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['유상증자', '경영권', '매수']</t>
+          <t>['유상증자', '주가', '대주주']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48750</v>
+        <v>48800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-4.79%</t>
+          <t>'-4.69%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G18" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H18" t="n">
         <v>38.34</v>
@@ -2082,7 +2082,7 @@
         <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>71829425400</v>
+        <v>72467963825</v>
       </c>
       <c r="P18" t="n">
         <v>67300</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81400</v>
+        <v>81800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.90%</t>
+          <t>'-5.43%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="F19" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G19" t="n">
-        <v>1616</v>
+        <v>1645</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2174,7 +2174,7 @@
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>238826426550</v>
+        <v>242760636450</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 관련 호재에도 불구하고 주가 하락 및 외인/기관 매도세 우려.</t>
+          <t>원전 관련 호재에도 불구하고 주가 하락에 대한 불만과 차트 분석이 제시됨.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', 'SMR']</t>
+          <t>['원전', '차트', '주가']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F20" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>857</v>
+        <v>886</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>122687185340</v>
+        <v>123693799680</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>공매도 세력과의 전쟁 선포 및 파산 기대감 표출.</t>
+          <t>공매도 세력의 파산 및 자금 부족을 주장하며 주가 부양을 기대하는 의견이 다수.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['공매도', '대차해지']</t>
+          <t>['공매도', '대차', '주가조작']</t>
         </is>
       </c>
       <c r="X20" t="n">

--- a/data/trending_integrated_20260923_12.xlsx
+++ b/data/trending_integrated_20260923_12.xlsx
@@ -610,7 +610,7 @@
         <v>2.65</v>
       </c>
       <c r="O2" t="n">
-        <v>31554236543</v>
+        <v>31590639623</v>
       </c>
       <c r="P2" t="n">
         <v>6950</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18160</v>
+        <v>18600</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.01%</t>
+          <t>'+19.85%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G3" t="n">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="H3" t="n">
         <v>0.6</v>
@@ -702,7 +702,7 @@
         <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>81647639535</v>
+        <v>83942003400</v>
       </c>
       <c r="P3" t="n">
         <v>34650</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14520</v>
+        <v>14470</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+11.69%</t>
+          <t>'+11.31%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>41</v>
       </c>
       <c r="G4" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H4" t="n">
         <v>0.86</v>
@@ -794,7 +794,7 @@
         <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>153261381340</v>
+        <v>154158035755</v>
       </c>
       <c r="P4" t="n">
         <v>25700</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18370</v>
+        <v>18160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.06%</t>
+          <t>'+9.79%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.15</v>
       </c>
       <c r="E5" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F5" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G5" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.77</v>
       </c>
       <c r="O5" t="n">
-        <v>285789843640</v>
+        <v>287953315130</v>
       </c>
       <c r="P5" t="n">
         <v>30550</v>
@@ -931,123 +931,123 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>218000</v>
+        <v>3850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.07%</t>
+          <t>'+3.36%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>-0.35</v>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="H6" t="n">
-        <v>75.51000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>211500</v>
+        <v>3725</v>
       </c>
       <c r="K6" t="n">
-        <v>217000</v>
+        <v>3740</v>
       </c>
       <c r="L6" t="n">
-        <v>220000</v>
+        <v>4200</v>
       </c>
       <c r="M6" t="n">
-        <v>216500</v>
+        <v>3705</v>
       </c>
       <c r="N6" t="n">
-        <v>75.5</v>
+        <v>0.96</v>
       </c>
       <c r="O6" t="n">
-        <v>711734515500</v>
+        <v>64026027000</v>
       </c>
       <c r="P6" t="n">
-        <v>243500</v>
+        <v>6300</v>
       </c>
       <c r="Q6" t="n">
-        <v>65000</v>
+        <v>1738</v>
       </c>
       <c r="R6" t="n">
-        <v>753000</v>
+        <v>-41000</v>
       </c>
       <c r="S6" t="n">
-        <v>-47000</v>
+        <v>-5000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
+          <t>급격한 주가 하락과 '물량 떠넘기기', '국장 쓰레기' 등 격한 비난이 나타남. 개인 투자자들의 공포 심리를 이용한 주포의 단기 시세 조작 의혹이 제기됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '우선주', '장기보유']</t>
+          <t>['주가하락', '단기매매', '공포']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>283250</v>
+        <v>218500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.44%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>486</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>1874</v>
+        <v>335</v>
       </c>
       <c r="H7" t="n">
-        <v>46.55</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,91 +1055,91 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>276500</v>
+        <v>211500</v>
       </c>
       <c r="K7" t="n">
-        <v>284500</v>
+        <v>217000</v>
       </c>
       <c r="L7" t="n">
-        <v>285000</v>
+        <v>220000</v>
       </c>
       <c r="M7" t="n">
-        <v>281000</v>
+        <v>216500</v>
       </c>
       <c r="N7" t="n">
-        <v>46.56</v>
+        <v>75.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2886839674750</v>
+        <v>732530995250</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q7" t="n">
-        <v>82400</v>
+        <v>65000</v>
       </c>
       <c r="R7" t="n">
-        <v>1744000</v>
+        <v>753000</v>
       </c>
       <c r="S7" t="n">
-        <v>499000</v>
+        <v>-47000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>정치적 발언과 함께 주가 상승 및 배당 관련 질문이 혼재됨.</t>
+          <t>장기 보유 및 배당 기대감, 우선주 강세 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['배당', '주가', '분석']</t>
+          <t>['배당', '우선주', '장기보유']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>112</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13920</v>
+        <v>283500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.53%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>41</v>
+        <v>483</v>
       </c>
       <c r="G8" t="n">
-        <v>203</v>
+        <v>1913</v>
       </c>
       <c r="H8" t="n">
-        <v>9.609999999999999</v>
+        <v>46.55</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,130 +1147,130 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>13600</v>
+        <v>276500</v>
       </c>
       <c r="K8" t="n">
-        <v>13750</v>
+        <v>284500</v>
       </c>
       <c r="L8" t="n">
-        <v>15050</v>
+        <v>285000</v>
       </c>
       <c r="M8" t="n">
-        <v>13740</v>
+        <v>281000</v>
       </c>
       <c r="N8" t="n">
-        <v>9.77</v>
+        <v>46.56</v>
       </c>
       <c r="O8" t="n">
-        <v>92829086855</v>
+        <v>2954304683250</v>
       </c>
       <c r="P8" t="n">
-        <v>23550</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>5780</v>
+        <v>82400</v>
       </c>
       <c r="R8" t="n">
-        <v>180000</v>
+        <v>1744000</v>
       </c>
       <c r="S8" t="n">
-        <v>-194000</v>
+        <v>499000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
+          <t>대통령 관련 정치적 언급과 함께 주가 상승에 대한 기대가 혼재하나, 구체적인 근거는 부족함. 단기적인 주가 등락에 대한 언급과 함께 배당 관련 문의가 나타남.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['기관', '외인', '주가조작']</t>
+          <t>['주가', '배당']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>112</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3780</v>
+        <v>13930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+1.48%</t>
+          <t>'+2.43%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.35</v>
+        <v>-0.16</v>
       </c>
       <c r="E9" t="n">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>357</v>
+        <v>202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.61</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3725</v>
+        <v>13600</v>
       </c>
       <c r="K9" t="n">
-        <v>3740</v>
+        <v>13750</v>
       </c>
       <c r="L9" t="n">
-        <v>4200</v>
+        <v>15050</v>
       </c>
       <c r="M9" t="n">
-        <v>3705</v>
+        <v>13740</v>
       </c>
       <c r="N9" t="n">
-        <v>0.96</v>
+        <v>9.77</v>
       </c>
       <c r="O9" t="n">
-        <v>63411007035</v>
+        <v>93207220080</v>
       </c>
       <c r="P9" t="n">
-        <v>6300</v>
+        <v>23550</v>
       </c>
       <c r="Q9" t="n">
-        <v>1738</v>
+        <v>5780</v>
       </c>
       <c r="R9" t="n">
-        <v>-41000</v>
+        <v>180000</v>
       </c>
       <c r="S9" t="n">
-        <v>-5000</v>
+        <v>-194000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>주가 급락 및 물량 넘기기에 대한 불만 표출.</t>
+          <t>기관 및 외인 매도세 지속, 주가 하락에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,20 +1279,20 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['기관', '외인', '주가조작']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>093370</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8550</v>
+        <v>8540</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.83%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H10" t="n">
         <v>26.63</v>
@@ -1346,7 +1346,7 @@
         <v>26.58</v>
       </c>
       <c r="O10" t="n">
-        <v>20647516100</v>
+        <v>20924425410</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>키움증권의 매매 행태와 주가 하락에 대한 불만이 제기되며, 일부 긍정적 전망도 존재.</t>
+          <t>키움증권의 매수·매도 공방 속에서 주가 상승 기대감과 함께 '물량 넘기기', '가짜 외인' 등 의혹이 제기됨. 유리 기판 사업 등 신사업에 대한 언급도 있음.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['주가조작', '외인', '전망']</t>
+          <t>['매매주체', '실적', '신사업']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1855000</v>
+        <v>1847000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.38%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="G11" t="n">
-        <v>1667</v>
+        <v>1692</v>
       </c>
       <c r="H11" t="n">
         <v>50.15</v>
@@ -1438,7 +1438,7 @@
         <v>50.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3386353901500</v>
+        <v>3454439024500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>국내 증시와 주가 관리 방식에 대한 불신이 강하게 나타나며, 반도체 시장과의 연동성 부족을 지적.</t>
+          <t>주가 관리 방식에 대한 불만과 함께 한국 증시의 신뢰도 하락, 미국 반도체 시장과의 격차 등에 대한 부정적 인식이 나타남. 기관 투신 연기금의 매수세 언급은 있으나 전반적으로 부정적인 분위기.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['주가', '국장', '반도체']</t>
+          <t>['주가관리', '증시', '반도체']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31100</v>
+        <v>31000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+0.16%</t>
+          <t>'-0.16%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1501,10 +1501,10 @@
         <v>270</v>
       </c>
       <c r="F12" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G12" t="n">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="H12" t="n">
         <v>16.63</v>
@@ -1530,7 +1530,7 @@
         <v>16.42</v>
       </c>
       <c r="O12" t="n">
-        <v>9339041525</v>
+        <v>9507858600</v>
       </c>
       <c r="P12" t="n">
         <v>69200</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 FDA 신약 승인 기대감 및 간암, 담관암 관련 긍정적 전망. 릴레이테라퓨틱스 상승 및 공매도 세력 언급.</t>
+          <t>미국 릴레이테라퓨틱스의 상승 마감과 FDA 승인 기대감이 고조됨. 간암 및 담관암 관련 임상 결과 발표에 대한 기대와 함께 단기 목표 주가 50만원, 글로벌 블록버스터 전망이 제시됨.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신약 승인', 'FDA', '간암']</t>
+          <t>['FDA승인', '임상결과', '블록버스터']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>0.62</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
         <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H13" t="n">
         <v>52.8</v>
@@ -1622,7 +1622,7 @@
         <v>25.75</v>
       </c>
       <c r="O13" t="n">
-        <v>86806276450</v>
+        <v>87737555650</v>
       </c>
       <c r="P13" t="n">
         <v>32100</v>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17690</v>
+        <v>17670</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.67%</t>
+          <t>'-0.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.76</v>
       </c>
       <c r="E14" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G14" t="n">
-        <v>763</v>
+        <v>780</v>
       </c>
       <c r="H14" t="n">
         <v>5.46</v>
@@ -1714,7 +1714,7 @@
         <v>6.22</v>
       </c>
       <c r="O14" t="n">
-        <v>123459195660</v>
+        <v>124311899865</v>
       </c>
       <c r="P14" t="n">
         <v>31500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30950</v>
+        <v>30750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.06%</t>
+          <t>'-2.69%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>0.4</v>
       </c>
       <c r="E15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
         <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H15" t="n">
         <v>11.7</v>
@@ -1806,7 +1806,7 @@
         <v>11.3</v>
       </c>
       <c r="O15" t="n">
-        <v>68913188500</v>
+        <v>70092874600</v>
       </c>
       <c r="P15" t="n">
         <v>75900</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23150</v>
+        <v>23100</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.08</v>
       </c>
       <c r="E16" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
         <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H16" t="n">
         <v>1.68</v>
@@ -1898,7 +1898,7 @@
         <v>1.76</v>
       </c>
       <c r="O16" t="n">
-        <v>67417620675</v>
+        <v>67690571200</v>
       </c>
       <c r="P16" t="n">
         <v>39350</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 소식과 함께 주가 상승에 대한 기대감이 있으나, 거래량 부족 및 주가 하락에 대한 우려도 존재.</t>
+          <t>타임지 선정 등 긍정적 재료 언급과 함께 향후 10만 원까지 상승할 것이라는 기대감이 있음. 그러나 거래량 감소 및 주가 변동성에 대한 의문도 제기되며, 코스피 시장 상황도 고려됨.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['타임지', '헬스테크', '주가']</t>
+          <t>['헬스케어', '주가전망', '거래량']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2780</v>
+        <v>2760</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.64%</t>
+          <t>'-4.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>0.92</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G17" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H17" t="n">
         <v>1.4</v>
@@ -1990,7 +1990,7 @@
         <v>0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>21731465807</v>
+        <v>21786853402</v>
       </c>
       <c r="P17" t="n">
         <v>4760</v>
@@ -2050,13 +2050,13 @@
         <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G18" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="H18" t="n">
         <v>38.34</v>
@@ -2082,7 +2082,7 @@
         <v>38.44</v>
       </c>
       <c r="O18" t="n">
-        <v>72467963825</v>
+        <v>73321323650</v>
       </c>
       <c r="P18" t="n">
         <v>67300</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>81800</v>
+        <v>81500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-5.43%</t>
+          <t>'-5.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.02</v>
       </c>
       <c r="E19" t="n">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="F19" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="G19" t="n">
-        <v>1645</v>
+        <v>1695</v>
       </c>
       <c r="H19" t="n">
         <v>23.03</v>
@@ -2174,7 +2174,7 @@
         <v>23.05</v>
       </c>
       <c r="O19" t="n">
-        <v>242760636450</v>
+        <v>252078915850</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>원전 관련 호재에도 불구하고 주가 하락에 대한 불만과 차트 분석이 제시됨.</t>
+          <t>한국형 원전 수출 확정 및 SMR 관련 긍정적 언급이 있으나, 외인·기관·연기금 매도와 차트 붕괴 등 부정적 전망이 우세함. 단기 조정 후 상승 가능성도 언급됨.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['원전', '차트', '주가']</t>
+          <t>['원전', 'SMR', '수급']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17590</v>
+        <v>17550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.44%</t>
+          <t>'-6.65%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.09</v>
       </c>
       <c r="E20" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F20" t="n">
         <v>108</v>
       </c>
       <c r="G20" t="n">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="H20" t="n">
         <v>10.38</v>
@@ -2266,7 +2266,7 @@
         <v>10.47</v>
       </c>
       <c r="O20" t="n">
-        <v>123693799680</v>
+        <v>125655706695</v>
       </c>
       <c r="P20" t="n">
         <v>40350</v>
